--- a/02_spreadsheet/spreadsheet_workbook.xlsx
+++ b/02_spreadsheet/spreadsheet_workbook.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shanu\Github\module2_assignment\02_spreadsheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E4007A-1BD5-4AF9-AB2F-2D27ECD6DA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA61460-574D-458F-988C-8F597FE6E457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="transactions_raw" sheetId="1" r:id="rId1"/>
+    <sheet name="merchant_master" sheetId="2" r:id="rId2"/>
+    <sheet name="exchange_rates" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">transactions_raw!$A$1:$O$31</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,8 +40,55 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="2">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+  <valueMetadata count="2">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+    <bk>
+      <rc t="2" v="1"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="133">
   <si>
     <t>transaction_id</t>
   </si>
@@ -351,6 +403,90 @@
   </si>
   <si>
     <t>score:47</t>
+  </si>
+  <si>
+    <t>merchant_id</t>
+  </si>
+  <si>
+    <t>account_manager</t>
+  </si>
+  <si>
+    <t>merchant_category</t>
+  </si>
+  <si>
+    <t>default_region</t>
+  </si>
+  <si>
+    <t>M001</t>
+  </si>
+  <si>
+    <t>Aisha Khan</t>
+  </si>
+  <si>
+    <t>Grocery</t>
+  </si>
+  <si>
+    <t>M002</t>
+  </si>
+  <si>
+    <t>Rohan Mehta</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>M003</t>
+  </si>
+  <si>
+    <t>Elena Rossi</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>M004</t>
+  </si>
+  <si>
+    <t>Marcus Lee</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>M005</t>
+  </si>
+  <si>
+    <t>Nina Weber</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>rate_date</t>
+  </si>
+  <si>
+    <t>usd_rate</t>
+  </si>
+  <si>
+    <t>merchant_name_cleaned</t>
+  </si>
+  <si>
+    <t>status_clean</t>
+  </si>
+  <si>
+    <t>risk_score_clean</t>
+  </si>
+  <si>
+    <t>gateway_region_clean</t>
+  </si>
+  <si>
+    <t>amount_usd</t>
+  </si>
+  <si>
+    <t>high_value_flag</t>
+  </si>
+  <si>
+    <t>high_risk_flag</t>
   </si>
 </sst>
 </file>
@@ -404,6 +540,74 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+  <rv s="0">
+    <fb t="e">#N/A</fb>
+    <v>6</v>
+    <v>7</v>
+  </rv>
+  <rv s="1">
+    <fb t="e">#N/A</fb>
+    <v>6</v>
+    <v>1</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="propagated" t="b"/>
+  </s>
+</rvStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -669,10 +873,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.54296875" customWidth="1"/>
+    <col min="11" max="11" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.1796875" customWidth="1"/>
+    <col min="13" max="13" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -680,958 +901,2526 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P1" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R1" t="s">
+        <v>107</v>
+      </c>
+      <c r="S1" t="s">
+        <v>131</v>
+      </c>
+      <c r="T1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1">
         <v>46082</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="str">
+        <f>PROPER(TRIM(D2))</f>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>420000</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" cm="1">
+        <f t="array" ref="G2">E2 * _xlfn.XLOOKUP(B2&amp;F2, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>4998</v>
+      </c>
+      <c r="H2" t="str">
+        <f>LOWER(TRIM(I2))</f>
+        <v>captured</v>
+      </c>
+      <c r="I2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" cm="1">
+        <f t="array" ref="J2">IF(TRIM(H2)="","",VALUE(_xlfn.REGEXEXTRACT(K2,"\d+")))</f>
+        <v>62</v>
+      </c>
+      <c r="K2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="str">
+        <f>IF(TRIM(M2)="", VLOOKUP(C2, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M2)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="M2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="N2" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P2" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C2, merchant_master!$B:$B, 0))</f>
+        <v>M001</v>
+      </c>
+      <c r="Q2" t="str">
+        <f>VLOOKUP(C2, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Aisha Khan</v>
+      </c>
+      <c r="R2" t="str">
+        <f>VLOOKUP(C2, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Grocery</v>
+      </c>
+      <c r="S2">
+        <f>IF(OR(AND(L2="APAC", G2&gt;5000), AND(L2="EU", G2&gt;6000), AND(L2="US", G2&gt;7000)), 1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <f>IF(OR(J2&gt;=70, ISNUMBER(SEARCH("chargeback", H2))), 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="1">
         <v>46082</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="str">
+        <f t="shared" ref="C3:C31" si="0">PROPER(TRIM(D3))</f>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>210000</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" cm="1">
+        <f t="array" ref="G3">E3 * _xlfn.XLOOKUP(B3&amp;F3, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>2499</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H31" si="1">LOWER(TRIM(I3))</f>
+        <v>captured</v>
+      </c>
+      <c r="I3" t="s">
         <v>20</v>
       </c>
-      <c r="G3">
+      <c r="J3" cm="1">
+        <f t="array" ref="J3">IF(TRIM(H3)="","",VALUE(_xlfn.REGEXEXTRACT(K3,"\d+")))</f>
         <v>55</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3">
+        <v>55</v>
+      </c>
+      <c r="L3" t="str">
+        <f>IF(TRIM(M3)="", VLOOKUP(C3, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M3)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="N3" t="s">
         <v>21</v>
       </c>
-      <c r="J3" t="s">
+      <c r="O3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P3" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C3, merchant_master!$B:$B, 0))</f>
+        <v>M001</v>
+      </c>
+      <c r="Q3" t="str">
+        <f>VLOOKUP(C3, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Aisha Khan</v>
+      </c>
+      <c r="R3" t="str">
+        <f>VLOOKUP(C3, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Grocery</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:S31" si="2">IF(OR(AND(L3="APAC", G3&gt;5000), AND(L3="EU", G3&gt;6000), AND(L3="US", G3&gt;7000)), 1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T31" si="3">IF(OR(J3&gt;=70, ISNUMBER(SEARCH("chargeback", H3))), 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
       <c r="B4" s="1">
         <v>46082</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>510000</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" cm="1">
+        <f t="array" ref="G4">E4 * _xlfn.XLOOKUP(B4&amp;F4, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>6069</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I4" t="s">
         <v>25</v>
       </c>
-      <c r="G4">
+      <c r="J4" cm="1">
+        <f t="array" ref="J4">IF(TRIM(H4)="","",VALUE(_xlfn.REGEXEXTRACT(K4,"\d+")))</f>
         <v>71</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4">
+        <v>71</v>
+      </c>
+      <c r="L4" t="str">
+        <f>IF(TRIM(M4)="", VLOOKUP(C4, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M4)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="M4" t="s">
         <v>26</v>
       </c>
-      <c r="I4" t="s">
+      <c r="N4" t="s">
         <v>27</v>
       </c>
-      <c r="J4" t="s">
+      <c r="O4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P4" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C4, merchant_master!$B:$B, 0))</f>
+        <v>M002</v>
+      </c>
+      <c r="Q4" t="str">
+        <f>VLOOKUP(C4, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Rohan Mehta</v>
+      </c>
+      <c r="R4" t="str">
+        <f>VLOOKUP(C4, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Electronics</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="1">
         <v>46083</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>160000</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" cm="1">
+        <f t="array" ref="G5">E5 * _xlfn.XLOOKUP(B5&amp;F5, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>1920</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="1"/>
+        <v>failed e05 timeout</v>
+      </c>
+      <c r="I5" t="s">
         <v>31</v>
       </c>
-      <c r="G5">
+      <c r="J5" cm="1">
+        <f t="array" ref="J5">IF(TRIM(H5)="","",VALUE(_xlfn.REGEXEXTRACT(K5,"\d+")))</f>
         <v>68</v>
       </c>
-      <c r="H5" t="s">
+      <c r="K5">
+        <v>68</v>
+      </c>
+      <c r="L5" t="str">
+        <f>IF(TRIM(M5)="", VLOOKUP(C5, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M5)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="M5" t="s">
         <v>32</v>
       </c>
-      <c r="I5" t="s">
+      <c r="N5" t="s">
         <v>33</v>
       </c>
-      <c r="J5" t="s">
+      <c r="O5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P5" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C5, merchant_master!$B:$B, 0))</f>
+        <v>M002</v>
+      </c>
+      <c r="Q5" t="str">
+        <f>VLOOKUP(C5, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Rohan Mehta</v>
+      </c>
+      <c r="R5" t="str">
+        <f>VLOOKUP(C5, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Electronics</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="1">
         <v>46083</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="D6" t="s">
         <v>35</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>390000</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>12</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" cm="1">
+        <f t="array" ref="G6">E6 * _xlfn.XLOOKUP(B6&amp;F6, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>4680</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I6" t="s">
         <v>25</v>
       </c>
-      <c r="G6">
+      <c r="J6" cm="1">
+        <f t="array" ref="J6">IF(TRIM(H6)="","",VALUE(_xlfn.REGEXEXTRACT(K6,"\d+")))</f>
         <v>58</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6">
+        <v>58</v>
+      </c>
+      <c r="L6" t="str">
+        <f>IF(TRIM(M6)="", VLOOKUP(C6, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M6)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="N6" t="s">
         <v>16</v>
       </c>
-      <c r="J6" t="s">
+      <c r="O6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P6" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C6, merchant_master!$B:$B, 0))</f>
+        <v>M001</v>
+      </c>
+      <c r="Q6" t="str">
+        <f>VLOOKUP(C6, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Aisha Khan</v>
+      </c>
+      <c r="R6" t="str">
+        <f>VLOOKUP(C6, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Grocery</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="1">
         <v>46083</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="D7" t="s">
         <v>30</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>275000</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" cm="1">
+        <f t="array" ref="G7">E7 * _xlfn.XLOOKUP(B7&amp;F7, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>3300</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I7" t="s">
         <v>20</v>
       </c>
-      <c r="G7" t="s">
+      <c r="J7" cm="1">
+        <f t="array" ref="J7">IF(TRIM(H7)="","",VALUE(_xlfn.REGEXEXTRACT(K7,"\d+")))</f>
+        <v>64</v>
+      </c>
+      <c r="K7" t="s">
         <v>37</v>
       </c>
-      <c r="I7" t="s">
+      <c r="L7" t="str">
+        <f>IF(TRIM(M7)="", VLOOKUP(C7, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M7)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="N7" t="s">
         <v>38</v>
       </c>
-      <c r="J7" t="s">
+      <c r="O7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P7" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C7, merchant_master!$B:$B, 0))</f>
+        <v>M002</v>
+      </c>
+      <c r="Q7" t="str">
+        <f>VLOOKUP(C7, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Rohan Mehta</v>
+      </c>
+      <c r="R7" t="str">
+        <f>VLOOKUP(C7, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Electronics</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="1">
         <v>46083</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="D8" t="s">
         <v>41</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>450000</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" cm="1">
+        <f t="array" ref="G8">E8 * _xlfn.XLOOKUP(B8&amp;F8, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>5400</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="1"/>
+        <v>chargeback</v>
+      </c>
+      <c r="I8" t="s">
         <v>42</v>
       </c>
-      <c r="G8" t="s">
+      <c r="J8" cm="1">
+        <f t="array" ref="J8">IF(TRIM(H8)="","",VALUE(_xlfn.REGEXEXTRACT(K8,"\d+")))</f>
+        <v>83</v>
+      </c>
+      <c r="K8" t="s">
         <v>43</v>
       </c>
-      <c r="H8" t="s">
+      <c r="L8" t="str">
+        <f>IF(TRIM(M8)="", VLOOKUP(C8, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M8)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="M8" t="s">
         <v>26</v>
       </c>
-      <c r="I8" t="s">
+      <c r="N8" t="s">
         <v>44</v>
       </c>
-      <c r="J8" t="s">
+      <c r="O8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P8" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C8, merchant_master!$B:$B, 0))</f>
+        <v>M001</v>
+      </c>
+      <c r="Q8" t="str">
+        <f>VLOOKUP(C8, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Aisha Khan</v>
+      </c>
+      <c r="R8" t="str">
+        <f>VLOOKUP(C8, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Grocery</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>45</v>
       </c>
       <c r="B9" s="1">
         <v>46084</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>340000</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>12</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" cm="1">
+        <f t="array" ref="G9">E9 * _xlfn.XLOOKUP(B9&amp;F9, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>4114</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I9" t="s">
         <v>20</v>
       </c>
-      <c r="G9">
+      <c r="J9" cm="1">
+        <f t="array" ref="J9">IF(TRIM(H9)="","",VALUE(_xlfn.REGEXEXTRACT(K9,"\d+")))</f>
         <v>59</v>
       </c>
-      <c r="I9" t="s">
+      <c r="K9">
+        <v>59</v>
+      </c>
+      <c r="L9" t="str">
+        <f>IF(TRIM(M9)="", VLOOKUP(C9, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M9)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="N9" t="s">
         <v>46</v>
       </c>
-      <c r="J9" t="s">
+      <c r="O9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P9" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C9, merchant_master!$B:$B, 0))</f>
+        <v>M002</v>
+      </c>
+      <c r="Q9" t="str">
+        <f>VLOOKUP(C9, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Rohan Mehta</v>
+      </c>
+      <c r="R9" t="str">
+        <f>VLOOKUP(C9, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Electronics</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>47</v>
       </c>
       <c r="B10" s="1">
         <v>46084</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="D10" t="s">
         <v>35</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>125000</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>12</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" cm="1">
+        <f t="array" ref="G10">E10 * _xlfn.XLOOKUP(B10&amp;F10, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>1512.5</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I10" t="s">
         <v>13</v>
       </c>
-      <c r="G10">
+      <c r="J10" cm="1">
+        <f t="array" ref="J10">IF(TRIM(H10)="","",VALUE(_xlfn.REGEXEXTRACT(K10,"\d+")))</f>
         <v>46</v>
       </c>
-      <c r="H10" t="s">
+      <c r="K10">
+        <v>46</v>
+      </c>
+      <c r="L10" t="str">
+        <f>IF(TRIM(M10)="", VLOOKUP(C10, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M10)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="M10" t="s">
         <v>15</v>
       </c>
-      <c r="I10" t="s">
+      <c r="N10" t="s">
         <v>21</v>
       </c>
-      <c r="J10" t="s">
+      <c r="O10" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P10" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C10, merchant_master!$B:$B, 0))</f>
+        <v>M001</v>
+      </c>
+      <c r="Q10" t="str">
+        <f>VLOOKUP(C10, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Aisha Khan</v>
+      </c>
+      <c r="R10" t="str">
+        <f>VLOOKUP(C10, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Grocery</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>48</v>
       </c>
       <c r="B11" s="1">
         <v>46084</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="D11" t="s">
         <v>49</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>610000</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>12</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" cm="1">
+        <f t="array" ref="G11">E11 * _xlfn.XLOOKUP(B11&amp;F11, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>7381</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I11" t="s">
         <v>13</v>
       </c>
-      <c r="G11" t="s">
+      <c r="J11" cm="1">
+        <f t="array" ref="J11">IF(TRIM(H11)="","",VALUE(_xlfn.REGEXEXTRACT(K11,"\d+")))</f>
+        <v>77</v>
+      </c>
+      <c r="K11" t="s">
         <v>50</v>
       </c>
-      <c r="I11" t="s">
+      <c r="L11" t="str">
+        <f>IF(TRIM(M11)="", VLOOKUP(C11, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M11)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="N11" t="s">
         <v>27</v>
       </c>
-      <c r="J11" t="s">
+      <c r="O11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P11" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C11, merchant_master!$B:$B, 0))</f>
+        <v>M002</v>
+      </c>
+      <c r="Q11" t="str">
+        <f>VLOOKUP(C11, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Rohan Mehta</v>
+      </c>
+      <c r="R11" t="str">
+        <f>VLOOKUP(C11, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Electronics</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>51</v>
       </c>
       <c r="B12" s="1">
         <v>46084</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="D12" t="s">
         <v>41</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>195000</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>12</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" cm="1">
+        <f t="array" ref="G12">E12 * _xlfn.XLOOKUP(B12&amp;F12, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>2359.5</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="1"/>
+        <v>failed e05 timeout</v>
+      </c>
+      <c r="I12" t="s">
         <v>52</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="e" cm="1" vm="1">
+        <f t="array" ref="J12">IF(TRIM(H12)="","",VALUE(_xlfn.REGEXEXTRACT(K12,"\d+")))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L12" t="str">
+        <f>IF(TRIM(M12)="", VLOOKUP(C12, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M12)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="N12" t="s">
         <v>53</v>
       </c>
-      <c r="J12" t="s">
+      <c r="O12" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P12" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C12, merchant_master!$B:$B, 0))</f>
+        <v>M001</v>
+      </c>
+      <c r="Q12" t="str">
+        <f>VLOOKUP(C12, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Aisha Khan</v>
+      </c>
+      <c r="R12" t="str">
+        <f>VLOOKUP(C12, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Grocery</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T12" t="e" vm="2">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>54</v>
       </c>
       <c r="B13" s="1">
         <v>46085</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="D13" t="s">
         <v>30</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>250000</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>12</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" cm="1">
+        <f t="array" ref="G13">E13 * _xlfn.XLOOKUP(B13&amp;F13, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>3000</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I13" t="s">
         <v>55</v>
       </c>
-      <c r="G13" t="s">
+      <c r="J13" cm="1">
+        <f t="array" ref="J13">IF(TRIM(H13)="","",VALUE(_xlfn.REGEXEXTRACT(K13,"\d+")))</f>
+        <v>61</v>
+      </c>
+      <c r="K13" t="s">
         <v>56</v>
       </c>
-      <c r="H13" t="s">
+      <c r="L13" t="str">
+        <f>IF(TRIM(M13)="", VLOOKUP(C13, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M13)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="M13" t="s">
         <v>26</v>
       </c>
-      <c r="I13" t="s">
+      <c r="N13" t="s">
         <v>57</v>
       </c>
-      <c r="J13" t="s">
+      <c r="O13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P13" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C13, merchant_master!$B:$B, 0))</f>
+        <v>M002</v>
+      </c>
+      <c r="Q13" t="str">
+        <f>VLOOKUP(C13, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Rohan Mehta</v>
+      </c>
+      <c r="R13" t="str">
+        <f>VLOOKUP(C13, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Electronics</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>58</v>
       </c>
       <c r="B14" s="1">
         <v>46085</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="D14" t="s">
         <v>11</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>310000</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>12</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" cm="1">
+        <f t="array" ref="G14">E14 * _xlfn.XLOOKUP(B14&amp;F14, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>3720</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I14" t="s">
         <v>55</v>
       </c>
-      <c r="G14" t="s">
+      <c r="J14" cm="1">
+        <f t="array" ref="J14">IF(TRIM(H14)="","",VALUE(_xlfn.REGEXEXTRACT(K14,"\d+")))</f>
+        <v>54</v>
+      </c>
+      <c r="K14" t="s">
         <v>59</v>
       </c>
-      <c r="H14" t="s">
+      <c r="L14" t="str">
+        <f>IF(TRIM(M14)="", VLOOKUP(C14, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M14)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="M14" t="s">
         <v>15</v>
       </c>
-      <c r="I14" t="s">
+      <c r="N14" t="s">
         <v>60</v>
       </c>
-      <c r="J14" t="s">
+      <c r="O14" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P14" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C14, merchant_master!$B:$B, 0))</f>
+        <v>M001</v>
+      </c>
+      <c r="Q14" t="str">
+        <f>VLOOKUP(C14, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Aisha Khan</v>
+      </c>
+      <c r="R14" t="str">
+        <f>VLOOKUP(C14, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Grocery</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>61</v>
       </c>
       <c r="B15" s="1">
         <v>46085</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="D15" t="s">
         <v>30</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>470000</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>12</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" cm="1">
+        <f t="array" ref="G15">E15 * _xlfn.XLOOKUP(B15&amp;F15, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>5640</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I15" t="s">
         <v>55</v>
       </c>
-      <c r="G15" t="s">
+      <c r="J15" cm="1">
+        <f t="array" ref="J15">IF(TRIM(H15)="","",VALUE(_xlfn.REGEXEXTRACT(K15,"\d+")))</f>
+        <v>73</v>
+      </c>
+      <c r="K15" t="s">
         <v>62</v>
       </c>
-      <c r="H15" t="s">
+      <c r="L15" t="str">
+        <f>IF(TRIM(M15)="", VLOOKUP(C15, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M15)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="M15" t="s">
         <v>15</v>
       </c>
-      <c r="I15" t="s">
+      <c r="N15" t="s">
         <v>16</v>
       </c>
-      <c r="J15" t="s">
+      <c r="O15" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P15" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C15, merchant_master!$B:$B, 0))</f>
+        <v>M002</v>
+      </c>
+      <c r="Q15" t="str">
+        <f>VLOOKUP(C15, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Rohan Mehta</v>
+      </c>
+      <c r="R15" t="str">
+        <f>VLOOKUP(C15, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Electronics</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>63</v>
       </c>
       <c r="B16" s="1">
         <v>46085</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="D16" t="s">
         <v>35</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>130000</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>12</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" cm="1">
+        <f t="array" ref="G16">E16 * _xlfn.XLOOKUP(B16&amp;F16, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>1560</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I16" t="s">
         <v>13</v>
       </c>
-      <c r="G16" t="s">
+      <c r="J16" cm="1">
+        <f t="array" ref="J16">IF(TRIM(H16)="","",VALUE(_xlfn.REGEXEXTRACT(K16,"\d+")))</f>
+        <v>52</v>
+      </c>
+      <c r="K16" t="s">
         <v>64</v>
       </c>
-      <c r="I16" t="s">
+      <c r="L16" t="str">
+        <f>IF(TRIM(M16)="", VLOOKUP(C16, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M16)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="N16" t="s">
         <v>21</v>
       </c>
-      <c r="J16" t="s">
+      <c r="O16" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P16" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C16, merchant_master!$B:$B, 0))</f>
+        <v>M001</v>
+      </c>
+      <c r="Q16" t="str">
+        <f>VLOOKUP(C16, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Aisha Khan</v>
+      </c>
+      <c r="R16" t="str">
+        <f>VLOOKUP(C16, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Grocery</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>65</v>
       </c>
       <c r="B17" s="1">
         <v>46086</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="D17" t="s">
         <v>30</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>220000</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>12</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" cm="1">
+        <f t="array" ref="G17">E17 * _xlfn.XLOOKUP(B17&amp;F17, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>2596</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="1"/>
+        <v>failed e05 timeout</v>
+      </c>
+      <c r="I17" t="s">
         <v>66</v>
       </c>
-      <c r="G17" t="s">
+      <c r="J17" cm="1">
+        <f t="array" ref="J17">IF(TRIM(H17)="","",VALUE(_xlfn.REGEXEXTRACT(K17,"\d+")))</f>
+        <v>69</v>
+      </c>
+      <c r="K17" t="s">
         <v>67</v>
       </c>
-      <c r="I17" t="s">
+      <c r="L17" t="str">
+        <f>IF(TRIM(M17)="", VLOOKUP(C17, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M17)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="N17" t="s">
         <v>53</v>
       </c>
-      <c r="J17" t="s">
+      <c r="O17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P17" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C17, merchant_master!$B:$B, 0))</f>
+        <v>M002</v>
+      </c>
+      <c r="Q17" t="str">
+        <f>VLOOKUP(C17, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Rohan Mehta</v>
+      </c>
+      <c r="R17" t="str">
+        <f>VLOOKUP(C17, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Electronics</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="1">
         <v>46086</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="D18" t="s">
         <v>30</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>180000</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>12</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" cm="1">
+        <f t="array" ref="G18">E18 * _xlfn.XLOOKUP(B18&amp;F18, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>2124</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="1"/>
+        <v>failed e05 timeout</v>
+      </c>
+      <c r="I18" t="s">
         <v>69</v>
       </c>
-      <c r="G18" t="s">
+      <c r="J18" cm="1">
+        <f t="array" ref="J18">IF(TRIM(H18)="","",VALUE(_xlfn.REGEXEXTRACT(K18,"\d+")))</f>
+        <v>72</v>
+      </c>
+      <c r="K18" t="s">
         <v>70</v>
       </c>
-      <c r="H18" t="s">
+      <c r="L18" t="str">
+        <f>IF(TRIM(M18)="", VLOOKUP(C18, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M18)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="M18" t="s">
         <v>32</v>
       </c>
-      <c r="I18" t="s">
+      <c r="N18" t="s">
         <v>53</v>
       </c>
-      <c r="J18" t="s">
+      <c r="O18" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P18" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C18, merchant_master!$B:$B, 0))</f>
+        <v>M002</v>
+      </c>
+      <c r="Q18" t="str">
+        <f>VLOOKUP(C18, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Rohan Mehta</v>
+      </c>
+      <c r="R18" t="str">
+        <f>VLOOKUP(C18, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Electronics</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>71</v>
       </c>
       <c r="B19" s="1">
         <v>46086</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="D19" t="s">
         <v>24</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>145000</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>12</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" cm="1">
+        <f t="array" ref="G19">E19 * _xlfn.XLOOKUP(B19&amp;F19, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>1711</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="1"/>
+        <v>chargeback</v>
+      </c>
+      <c r="I19" t="s">
         <v>72</v>
       </c>
-      <c r="G19" t="s">
+      <c r="J19" cm="1">
+        <f t="array" ref="J19">IF(TRIM(H19)="","",VALUE(_xlfn.REGEXEXTRACT(K19,"\d+")))</f>
+        <v>86</v>
+      </c>
+      <c r="K19" t="s">
         <v>73</v>
       </c>
-      <c r="H19" t="s">
+      <c r="L19" t="str">
+        <f>IF(TRIM(M19)="", VLOOKUP(C19, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M19)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="M19" t="s">
         <v>26</v>
       </c>
-      <c r="I19" t="s">
+      <c r="N19" t="s">
         <v>53</v>
       </c>
-      <c r="J19" t="s">
+      <c r="O19" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P19" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C19, merchant_master!$B:$B, 0))</f>
+        <v>M002</v>
+      </c>
+      <c r="Q19" t="str">
+        <f>VLOOKUP(C19, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Rohan Mehta</v>
+      </c>
+      <c r="R19" t="str">
+        <f>VLOOKUP(C19, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Electronics</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>74</v>
       </c>
       <c r="B20" s="1">
         <v>46086</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="D20" t="s">
         <v>41</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>260000</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>12</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" cm="1">
+        <f t="array" ref="G20">E20 * _xlfn.XLOOKUP(B20&amp;F20, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>3068</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="1"/>
+        <v>failed e05 timeout</v>
+      </c>
+      <c r="I20" t="s">
         <v>69</v>
       </c>
-      <c r="G20" t="s">
+      <c r="J20" cm="1">
+        <f t="array" ref="J20">IF(TRIM(H20)="","",VALUE(_xlfn.REGEXEXTRACT(K20,"\d+")))</f>
+        <v>67</v>
+      </c>
+      <c r="K20" t="s">
         <v>75</v>
       </c>
-      <c r="H20" t="s">
+      <c r="L20" t="str">
+        <f>IF(TRIM(M20)="", VLOOKUP(C20, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M20)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="M20" t="s">
         <v>32</v>
       </c>
-      <c r="I20" t="s">
+      <c r="N20" t="s">
         <v>53</v>
       </c>
-      <c r="J20" t="s">
+      <c r="O20" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P20" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C20, merchant_master!$B:$B, 0))</f>
+        <v>M001</v>
+      </c>
+      <c r="Q20" t="str">
+        <f>VLOOKUP(C20, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Aisha Khan</v>
+      </c>
+      <c r="R20" t="str">
+        <f>VLOOKUP(C20, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Grocery</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>76</v>
       </c>
       <c r="B21" s="1">
         <v>46086</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="D21" t="s">
         <v>35</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>520000</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>12</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" cm="1">
+        <f t="array" ref="G21">E21 * _xlfn.XLOOKUP(B21&amp;F21, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>6136</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I21" t="s">
         <v>20</v>
       </c>
-      <c r="G21">
+      <c r="J21" cm="1">
+        <f t="array" ref="J21">IF(TRIM(H21)="","",VALUE(_xlfn.REGEXEXTRACT(K21,"\d+")))</f>
         <v>75</v>
       </c>
-      <c r="H21" t="s">
+      <c r="K21">
+        <v>75</v>
+      </c>
+      <c r="L21" t="str">
+        <f>IF(TRIM(M21)="", VLOOKUP(C21, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M21)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="M21" t="s">
         <v>15</v>
       </c>
-      <c r="I21" t="s">
+      <c r="N21" t="s">
         <v>38</v>
       </c>
-      <c r="J21" t="s">
+      <c r="O21" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P21" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C21, merchant_master!$B:$B, 0))</f>
+        <v>M001</v>
+      </c>
+      <c r="Q21" t="str">
+        <f>VLOOKUP(C21, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Aisha Khan</v>
+      </c>
+      <c r="R21" t="str">
+        <f>VLOOKUP(C21, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Grocery</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>77</v>
       </c>
       <c r="B22" s="1">
         <v>46087</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="D22" t="s">
         <v>78</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>330000</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>12</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" cm="1">
+        <f t="array" ref="G22">E22 * _xlfn.XLOOKUP(B22&amp;F22, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>3927.0000000000005</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I22" t="s">
         <v>55</v>
       </c>
-      <c r="G22" t="s">
+      <c r="J22" cm="1">
+        <f t="array" ref="J22">IF(TRIM(H22)="","",VALUE(_xlfn.REGEXEXTRACT(K22,"\d+")))</f>
+        <v>63</v>
+      </c>
+      <c r="K22" t="s">
         <v>79</v>
       </c>
-      <c r="I22" t="s">
+      <c r="L22" t="str">
+        <f>IF(TRIM(M22)="", VLOOKUP(C22, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M22)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="N22" t="s">
         <v>44</v>
       </c>
-      <c r="J22" t="s">
+      <c r="O22" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P22" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C22, merchant_master!$B:$B, 0))</f>
+        <v>M002</v>
+      </c>
+      <c r="Q22" t="str">
+        <f>VLOOKUP(C22, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Rohan Mehta</v>
+      </c>
+      <c r="R22" t="str">
+        <f>VLOOKUP(C22, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Electronics</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>80</v>
       </c>
       <c r="B23" s="1">
         <v>46087</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="D23" t="s">
         <v>19</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>410000</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>12</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" cm="1">
+        <f t="array" ref="G23">E23 * _xlfn.XLOOKUP(B23&amp;F23, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>4879</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I23" t="s">
         <v>55</v>
       </c>
-      <c r="G23">
+      <c r="J23" cm="1">
+        <f t="array" ref="J23">IF(TRIM(H23)="","",VALUE(_xlfn.REGEXEXTRACT(K23,"\d+")))</f>
         <v>60</v>
       </c>
-      <c r="H23" t="s">
+      <c r="K23">
+        <v>60</v>
+      </c>
+      <c r="L23" t="str">
+        <f>IF(TRIM(M23)="", VLOOKUP(C23, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M23)))</f>
+        <v>APAC</v>
+      </c>
+      <c r="M23" t="s">
         <v>15</v>
       </c>
-      <c r="I23" t="s">
+      <c r="N23" t="s">
         <v>46</v>
       </c>
-      <c r="J23" t="s">
+      <c r="O23" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P23" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C23, merchant_master!$B:$B, 0))</f>
+        <v>M001</v>
+      </c>
+      <c r="Q23" t="str">
+        <f>VLOOKUP(C23, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Aisha Khan</v>
+      </c>
+      <c r="R23" t="str">
+        <f>VLOOKUP(C23, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Grocery</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>81</v>
       </c>
       <c r="B24" s="1">
         <v>46082</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>City Pharma</v>
+      </c>
+      <c r="D24" t="s">
         <v>82</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>5200</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>83</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" cm="1">
+        <f t="array" ref="G24">E24 * _xlfn.XLOOKUP(B24&amp;F24, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>5616</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I24" t="s">
         <v>20</v>
       </c>
-      <c r="G24">
+      <c r="J24" cm="1">
+        <f t="array" ref="J24">IF(TRIM(H24)="","",VALUE(_xlfn.REGEXEXTRACT(K24,"\d+")))</f>
         <v>42</v>
       </c>
-      <c r="H24" t="s">
+      <c r="K24">
+        <v>42</v>
+      </c>
+      <c r="L24" t="str">
+        <f>IF(TRIM(M24)="", VLOOKUP(C24, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M24)))</f>
+        <v>EU</v>
+      </c>
+      <c r="M24" t="s">
         <v>84</v>
       </c>
-      <c r="I24" t="s">
+      <c r="N24" t="s">
         <v>27</v>
       </c>
-      <c r="J24" t="s">
+      <c r="O24" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P24" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C24, merchant_master!$B:$B, 0))</f>
+        <v>M003</v>
+      </c>
+      <c r="Q24" t="str">
+        <f>VLOOKUP(C24, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Elena Rossi</v>
+      </c>
+      <c r="R24" t="str">
+        <f>VLOOKUP(C24, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Healthcare</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>85</v>
       </c>
       <c r="B25" s="1">
         <v>46083</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Eco Home</v>
+      </c>
+      <c r="D25" t="s">
         <v>86</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>6100</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>83</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" cm="1">
+        <f t="array" ref="G25">E25 * _xlfn.XLOOKUP(B25&amp;F25, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>6649.0000000000009</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="1"/>
+        <v>chargeback</v>
+      </c>
+      <c r="I25" t="s">
         <v>72</v>
       </c>
-      <c r="G25" t="s">
+      <c r="J25" cm="1">
+        <f t="array" ref="J25">IF(TRIM(H25)="","",VALUE(_xlfn.REGEXEXTRACT(K25,"\d+")))</f>
+        <v>65</v>
+      </c>
+      <c r="K25" t="s">
         <v>87</v>
       </c>
-      <c r="H25" t="s">
+      <c r="L25" t="str">
+        <f>IF(TRIM(M25)="", VLOOKUP(C25, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M25)))</f>
+        <v>EU</v>
+      </c>
+      <c r="M25" t="s">
         <v>88</v>
       </c>
-      <c r="I25" t="s">
+      <c r="N25" t="s">
         <v>33</v>
       </c>
-      <c r="J25" t="s">
+      <c r="O25" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P25" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C25, merchant_master!$B:$B, 0))</f>
+        <v>M005</v>
+      </c>
+      <c r="Q25" t="str">
+        <f>VLOOKUP(C25, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Nina Weber</v>
+      </c>
+      <c r="R25" t="str">
+        <f>VLOOKUP(C25, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Home</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>89</v>
       </c>
       <c r="B26" s="1">
         <v>46084</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>City Pharma</v>
+      </c>
+      <c r="D26" t="s">
         <v>82</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>2800</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>83</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" cm="1">
+        <f t="array" ref="G26">E26 * _xlfn.XLOOKUP(B26&amp;F26, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>3024</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I26" t="s">
         <v>55</v>
       </c>
-      <c r="G26">
+      <c r="J26" cm="1">
+        <f t="array" ref="J26">IF(TRIM(H26)="","",VALUE(_xlfn.REGEXEXTRACT(K26,"\d+")))</f>
         <v>38</v>
       </c>
-      <c r="H26" t="s">
+      <c r="K26">
+        <v>38</v>
+      </c>
+      <c r="L26" t="str">
+        <f>IF(TRIM(M26)="", VLOOKUP(C26, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M26)))</f>
+        <v>EU</v>
+      </c>
+      <c r="M26" t="s">
         <v>90</v>
       </c>
-      <c r="I26" t="s">
+      <c r="N26" t="s">
         <v>38</v>
       </c>
-      <c r="J26" t="s">
+      <c r="O26" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P26" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C26, merchant_master!$B:$B, 0))</f>
+        <v>M003</v>
+      </c>
+      <c r="Q26" t="str">
+        <f>VLOOKUP(C26, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Elena Rossi</v>
+      </c>
+      <c r="R26" t="str">
+        <f>VLOOKUP(C26, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Healthcare</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>91</v>
       </c>
       <c r="B27" s="1">
         <v>46086</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Eco Home</v>
+      </c>
+      <c r="D27" t="s">
         <v>86</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>3300</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>83</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" cm="1">
+        <f t="array" ref="G27">E27 * _xlfn.XLOOKUP(B27&amp;F27, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>3597.0000000000005</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="1"/>
+        <v>failed e05 timeout</v>
+      </c>
+      <c r="I27" t="s">
         <v>69</v>
       </c>
-      <c r="G27">
+      <c r="J27" cm="1">
+        <f t="array" ref="J27">IF(TRIM(H27)="","",VALUE(_xlfn.REGEXEXTRACT(K27,"\d+")))</f>
         <v>44</v>
       </c>
-      <c r="H27" t="s">
+      <c r="K27">
+        <v>44</v>
+      </c>
+      <c r="L27" t="str">
+        <f>IF(TRIM(M27)="", VLOOKUP(C27, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M27)))</f>
+        <v>EU</v>
+      </c>
+      <c r="M27" t="s">
         <v>84</v>
       </c>
-      <c r="I27" t="s">
+      <c r="N27" t="s">
         <v>44</v>
       </c>
-      <c r="J27" t="s">
+      <c r="O27" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P27" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C27, merchant_master!$B:$B, 0))</f>
+        <v>M005</v>
+      </c>
+      <c r="Q27" t="str">
+        <f>VLOOKUP(C27, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Nina Weber</v>
+      </c>
+      <c r="R27" t="str">
+        <f>VLOOKUP(C27, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Home</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>92</v>
       </c>
       <c r="B28" s="1">
         <v>46082</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Delta Travels</v>
+      </c>
+      <c r="D28" t="s">
         <v>93</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>7200</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>94</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" cm="1">
+        <f t="array" ref="G28">E28 * _xlfn.XLOOKUP(B28&amp;F28, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>7200</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I28" t="s">
         <v>55</v>
       </c>
-      <c r="G28">
+      <c r="J28" cm="1">
+        <f t="array" ref="J28">IF(TRIM(H28)="","",VALUE(_xlfn.REGEXEXTRACT(K28,"\d+")))</f>
         <v>49</v>
       </c>
-      <c r="H28" t="s">
+      <c r="K28">
+        <v>49</v>
+      </c>
+      <c r="L28" t="str">
+        <f>IF(TRIM(M28)="", VLOOKUP(C28, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M28)))</f>
+        <v>US</v>
+      </c>
+      <c r="M28" t="s">
         <v>95</v>
       </c>
-      <c r="I28" t="s">
+      <c r="N28" t="s">
         <v>46</v>
       </c>
-      <c r="J28" t="s">
+      <c r="O28" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P28" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C28, merchant_master!$B:$B, 0))</f>
+        <v>M004</v>
+      </c>
+      <c r="Q28" t="str">
+        <f>VLOOKUP(C28, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Marcus Lee</v>
+      </c>
+      <c r="R28" t="str">
+        <f>VLOOKUP(C28, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Travel</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>96</v>
       </c>
       <c r="B29" s="1">
         <v>46083</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Delta Travels</v>
+      </c>
+      <c r="D29" t="s">
         <v>97</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>3100</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>94</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" cm="1">
+        <f t="array" ref="G29">E29 * _xlfn.XLOOKUP(B29&amp;F29, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>3100</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="1"/>
+        <v>captured</v>
+      </c>
+      <c r="I29" t="s">
         <v>25</v>
       </c>
-      <c r="G29" t="s">
+      <c r="J29" cm="1">
+        <f t="array" ref="J29">IF(TRIM(H29)="","",VALUE(_xlfn.REGEXEXTRACT(K29,"\d+")))</f>
+        <v>41</v>
+      </c>
+      <c r="K29" t="s">
         <v>98</v>
       </c>
-      <c r="H29" t="s">
+      <c r="L29" t="str">
+        <f>IF(TRIM(M29)="", VLOOKUP(C29, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M29)))</f>
+        <v>US</v>
+      </c>
+      <c r="M29" t="s">
         <v>99</v>
       </c>
-      <c r="I29" t="s">
+      <c r="N29" t="s">
         <v>53</v>
       </c>
-      <c r="J29" t="s">
+      <c r="O29" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P29" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C29, merchant_master!$B:$B, 0))</f>
+        <v>M004</v>
+      </c>
+      <c r="Q29" t="str">
+        <f>VLOOKUP(C29, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Marcus Lee</v>
+      </c>
+      <c r="R29" t="str">
+        <f>VLOOKUP(C29, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Travel</v>
+      </c>
+      <c r="S29">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>100</v>
       </c>
       <c r="B30" s="1">
         <v>46085</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Delta Travels</v>
+      </c>
+      <c r="D30" t="s">
         <v>101</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>2500</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>94</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" cm="1">
+        <f t="array" ref="G30">E30 * _xlfn.XLOOKUP(B30&amp;F30, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>2500</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="1"/>
+        <v>chargeback</v>
+      </c>
+      <c r="I30" t="s">
         <v>72</v>
       </c>
-      <c r="G30" t="s">
+      <c r="J30" cm="1">
+        <f t="array" ref="J30">IF(TRIM(H30)="","",VALUE(_xlfn.REGEXEXTRACT(K30,"\d+")))</f>
+        <v>58</v>
+      </c>
+      <c r="K30" t="s">
         <v>102</v>
       </c>
-      <c r="H30" t="s">
+      <c r="L30" t="str">
+        <f>IF(TRIM(M30)="", VLOOKUP(C30, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M30)))</f>
+        <v>US</v>
+      </c>
+      <c r="M30" t="s">
         <v>99</v>
       </c>
-      <c r="I30" t="s">
+      <c r="N30" t="s">
         <v>57</v>
       </c>
-      <c r="J30" t="s">
+      <c r="O30" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P30" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C30, merchant_master!$B:$B, 0))</f>
+        <v>M004</v>
+      </c>
+      <c r="Q30" t="str">
+        <f>VLOOKUP(C30, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Marcus Lee</v>
+      </c>
+      <c r="R30" t="str">
+        <f>VLOOKUP(C30, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Travel</v>
+      </c>
+      <c r="S30">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>103</v>
       </c>
       <c r="B31" s="1">
         <v>46087</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Delta Travels</v>
+      </c>
+      <c r="D31" t="s">
         <v>93</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>1800</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>94</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" cm="1">
+        <f t="array" ref="G31">E31 * _xlfn.XLOOKUP(B31&amp;F31, exchange_rates!$A:$A&amp;exchange_rates!$B:$B, exchange_rates!$C:$C)</f>
+        <v>1800</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="1"/>
+        <v>failed e05 timeout</v>
+      </c>
+      <c r="I31" t="s">
         <v>69</v>
       </c>
-      <c r="G31" t="s">
+      <c r="J31" cm="1">
+        <f t="array" ref="J31">IF(TRIM(H31)="","",VALUE(_xlfn.REGEXEXTRACT(K31,"\d+")))</f>
+        <v>47</v>
+      </c>
+      <c r="K31" t="s">
         <v>104</v>
       </c>
-      <c r="H31" t="s">
+      <c r="L31" t="str">
+        <f>IF(TRIM(M31)="", VLOOKUP(C31, merchant_master!$B:$E, 4, FALSE), UPPER(TRIM(M31)))</f>
+        <v>US</v>
+      </c>
+      <c r="M31" t="s">
         <v>99</v>
       </c>
-      <c r="I31" t="s">
+      <c r="N31" t="s">
         <v>60</v>
       </c>
-      <c r="J31" t="s">
+      <c r="O31" t="s">
         <v>17</v>
+      </c>
+      <c r="P31" t="str">
+        <f>INDEX(merchant_master!$A:$A, MATCH(C31, merchant_master!$B:$B, 0))</f>
+        <v>M004</v>
+      </c>
+      <c r="Q31" t="str">
+        <f>VLOOKUP(C31, merchant_master!$B:$E, 2, FALSE)</f>
+        <v>Marcus Lee</v>
+      </c>
+      <c r="R31" t="str">
+        <f>VLOOKUP(C31, merchant_master!$B:$E, 3, FALSE)</f>
+        <v>Travel</v>
+      </c>
+      <c r="S31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{485E719A-08BB-4891-9291-710EB6CA8D5F}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF992036-700C-437B-A63A-BAA34121CE5B}">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>1.1900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>1.21E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>1.18E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>1.1900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
